--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -56,7 +56,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,15 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,12 +100,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3F7FA"/>
         <bgColor rgb="00F3F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,37 +197,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -592,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -612,7 +618,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ご提供いただいたキックオフ会議資料（更新版・令和8年7月27日現在・第2稿）を、現時点の作業状況及び業務仕様書と照合しました。修正が必要な箇所12件（重大3・中6・軽微3）を確認しています。青枠の注記8箇所については、全件削除ではなく性格別の仕分けを提案します。作成日：令和8年7月31日。</t>
+          <t>ご提供いただいたキックオフ会議資料（更新版・令和8年7月27日現在・第2稿）を、現時点の作業状況及び業務仕様書と照合しました。修正が必要な箇所12件（重大3・中6・軽微3）を確認しました。青枠の注記8箇所については、全件削除ではなく性格別の仕分けを提案し、ご了承をいただきました。12件すべてと青枠の仕分けを反映した第3稿を作成しています。作成日：令和8年7月31日。</t>
         </is>
       </c>
     </row>
@@ -848,22 +854,157 @@
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="8" t="n"/>
     </row>
-    <row r="18" ht="104" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>【反映の結果（令和8年7月31日）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>ご指示</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>①事業所実態調査は仕様書に基づき削除、②再基準化は解消済みのため削除、③調整済認定率18.4％は撤回済みで了承、青枠は全件削除ではなく推奨の仕分けにより修正。</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>作成した資料</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>キックオフ会議資料 第3稿（第10期計画_キックオフ会議資料_第3稿.docx）。94段落18表。青枠は8箇所から2箇所（アジェンダ・まとめ）へ。</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>①の反映</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>6章の表題を「調査結果・事業所実態調査の活用方針」から「調査結果の活用方針」に改め、仕様書４（3）の対象4調査と、新たな調査の企画・設計・配布・回収・入力及び督促を行わない旨を本文に明記した。表1・表4・表6・表8・表10・表11・表15・表16・表17及び会議後の重点行動から、同調査を前提とする記述を削除した。供給可能量・受入困難・休廃止縮小意向・ICT・BCPが同調査によらなければ把握できないことは6章に注記し、実施の要否をヒアリングシート項目1で確認する形とした。</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>②の反映</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>7章の起点差の記述を削除し、階級別人口を実績人口×社人研推計の伸び率により求めることで基準年度の推計値が実績1,984人と一致する旨に改めた。8章の手順1・2、10章の工程表、まとめから「再基準化」の記述を削除した。あわせて認定者数の3シナリオの算定結果を7章に追加した。</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>③の反映</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>5章に「第10期KPIの基本案」の表を新設し（青枠 表7からの格上げ）、H01の測定指標を見える化W144（9.25％）とすること、18.4％はB5-a【注目する地域のみ】系列で全国・北海道と比較できないため撤回したことを明記した。表7（分析領域）・表12（成果物）の記述も改めた。</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>青枠の反映</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>残す2（表0 アジェンダ・表21 まとめ。内容を更新）、格上げ1（表7 KPIの基本案 → 5章の通常の表）、本文へ統合3（表3 整合の基本方針 → 3章本文、表5 進め方の原則 → 4章本文、表12 12月までに必要な状態 → 10章の注）、ヒアリングシートへ移行2（表9 → 6章に参照を記載、表14 → 9章に参照を記載）。</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>中6件・軽微3件</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="28" ht="104" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」に主張ごとに示しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="16">
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B22:E22"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -937,7 +1078,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
@@ -967,7 +1108,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
@@ -997,7 +1138,7 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
@@ -1027,7 +1168,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1057,7 +1198,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1087,7 +1228,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1117,7 +1258,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1147,7 +1288,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1177,7 +1318,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1207,7 +1348,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
@@ -1237,7 +1378,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
@@ -1267,7 +1408,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
@@ -1314,7 +1455,7 @@
       <c r="F18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
@@ -1332,7 +1473,7 @@
       <c r="F19" s="8" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1350,7 +1491,7 @@
       <c r="F20" s="8" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
@@ -1368,7 +1509,7 @@
       <c r="F21" s="8" t="n"/>
     </row>
     <row r="23" ht="104" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>注1）重大3件は、いずれも会議の前に方針をご確認いただきたい事項です。No.1は業務範囲、No.2は工程、No.3は指標の定義に関わります。注2）中6件・軽微3件は、受託者において資料を修正いたします。ご指示をいただければ第3稿として作成いたします。注3）修正の要否は資料の性格にもよります。会議で口頭により補足する前提であれば、軽微3件は修正せずに進めることもできます。</t>
         </is>
@@ -1444,7 +1585,7 @@
       </c>
     </row>
     <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>表0</t>
         </is>
@@ -1459,7 +1600,7 @@
           <t>会議のアジェンダ</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>残す（内容を更新）</t>
         </is>
@@ -1471,7 +1612,7 @@
       </c>
     </row>
     <row r="6" ht="76" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>表3</t>
         </is>
@@ -1486,7 +1627,7 @@
           <t>3章本文の要約（重複）</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>本文へ統合</t>
         </is>
@@ -1498,7 +1639,7 @@
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>表5</t>
         </is>
@@ -1513,7 +1654,7 @@
           <t>1行のみ。4章本文の要約（重複）</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>本文へ統合</t>
         </is>
@@ -1525,7 +1666,7 @@
       </c>
     </row>
     <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>表7</t>
         </is>
@@ -1540,7 +1681,7 @@
           <t>提案の実質的な内容</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>通常の表へ格上げ</t>
         </is>
@@ -1552,7 +1693,7 @@
       </c>
     </row>
     <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>表9</t>
         </is>
@@ -1567,7 +1708,7 @@
           <t>ヒアリング事項そのもの</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>ヒアリングシートへ移行</t>
         </is>
@@ -1579,7 +1720,7 @@
       </c>
     </row>
     <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>表12</t>
         </is>
@@ -1594,7 +1735,7 @@
           <t>到達目標</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>工程表（表15）の注へ統合</t>
         </is>
@@ -1606,7 +1747,7 @@
       </c>
     </row>
     <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>表14</t>
         </is>
@@ -1621,7 +1762,7 @@
           <t>運用ルール（合意事項）</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>ヒアリングシートへ移行</t>
         </is>
@@ -1633,7 +1774,7 @@
       </c>
     </row>
     <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>表21</t>
         </is>
@@ -1648,7 +1789,7 @@
           <t>総括</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>残す（内容を更新）</t>
         </is>
@@ -1690,7 +1831,7 @@
       </c>
     </row>
     <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>残す（内容を更新）</t>
         </is>
@@ -1711,7 +1852,7 @@
       </c>
     </row>
     <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>通常の表へ格上げ</t>
         </is>
@@ -1732,7 +1873,7 @@
       </c>
     </row>
     <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>本文へ統合</t>
         </is>
@@ -1753,7 +1894,7 @@
       </c>
     </row>
     <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>ヒアリングシートへ移行</t>
         </is>
@@ -1848,7 +1989,7 @@
       <c r="E26" s="8" t="n"/>
     </row>
     <row r="28" ht="104" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>注1）ヒアリングシートは別冊として作成しました（第10期計画_キックオフ会議ヒアリングシート.docx）。表9・表14の内容に加え、表18の確認事項5件、及び現時点で最も急ぐ決定事項を統合し、12項目としています。注2）青枠を残す場合の色（F3F7FA）は薄い青であり、白黒印刷では罫線のみが残ります。印刷を前提とする場合、枠線の太さで区別する方が確実です。注3）本シートの提案はあくまで案です。会議の進め方によっては、青枠を残したまま口頭で補足する方がよい場合もあります。</t>
         </is>
@@ -1934,7 +2075,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>事業所実態調査の実施</t>
         </is>
@@ -1959,7 +2100,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>代表KPIのデータ源</t>
         </is>
@@ -1984,7 +2125,7 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>個票データの取扱い</t>
         </is>
@@ -2006,7 +2147,7 @@
       </c>
     </row>
     <row r="9" ht="104" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>注1）No.1は、資料の修正にとどまらず業務範囲の確認を伴います。受託者としては、仕様書の範囲外の作業を無償で行う前提の工程を資料に残すことは適切でないと考えます。実施の要否と、実施する場合の取扱いをご確認ください。注2）事業所実態調査を実施しない場合でも、供給可能量の把握は可能です。見える化のK系列（事業所数）・M系列（従事者数）・D25〜D30（定員）に加え、3町の指定台帳又は施設への照会により把握します。ただし、受入困難・休廃止縮小意向・ICT・BCPは事業所への照会でしか把握できません。注3）これらはいずれも確認事項として既に整理しており、「必要事項の一覧」に登録しています。本シートは、キックオフ資料の記述との対応を示すものです。</t>
         </is>
@@ -2088,7 +2229,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>業務範囲</t>
         </is>
@@ -2118,7 +2259,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>日程</t>
         </is>
@@ -2148,7 +2289,7 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
@@ -2178,7 +2319,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
@@ -2208,7 +2349,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
@@ -2238,7 +2379,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>決定</t>
         </is>
@@ -2268,7 +2409,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>決定</t>
         </is>
@@ -2298,7 +2439,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>決定</t>
         </is>
@@ -2328,7 +2469,7 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>調査データ</t>
         </is>
@@ -2358,7 +2499,7 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>個人情報</t>
         </is>
@@ -2388,7 +2529,7 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
@@ -2418,7 +2559,7 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
@@ -2636,7 +2777,7 @@
       </c>
     </row>
     <row r="27" ht="104" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>注1）所要の合計は90分です。会議時間が限られる場合は、No.1・No.2・No.7を優先してください。この3件は、いずれも他の作業の前提となります。注2）ヒアリングシート（別冊）は、1項目1枠で確認内容・選択肢・記入欄・影響を構成しています。会議中に記入いただき、そのまま記録として残ります。注3）本シートに掲げた12項目は、「必要事項の一覧」に登録済みの事項から、会議で確認すべきものを抜き出したものです。全体の必要事項は同表をご覧ください。</t>
         </is>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_青枠の注記の扱い" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_業務範囲との齟齬" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ヒアリングシートへ移す事項" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_第3稿のレッドチームレビュー" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -757,52 +758,64 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>05_第3稿のレッドチームレビュー</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>受託者が作成した第3稿を批判的に点検する。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>12件（重大2・中7・軽微3）。うち5件は、分析資料では留保を付けていたのに会議資料に転記する際に留保が落ちたものである。12件すべてを第3稿に反映済み。</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>12件</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>【全体の所見】</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>観点</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>資料の構成</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>13章立て・22表の構成は適切です。会議の流れ（位置付け→業務→評価→調査→分析→見込量→協議→工程→成果物→確認事項→個人情報）に沿っており、この構成を変える必要はありません。</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>最も急ぐ修正</t>
+          <t>資料の構成</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>事業所実態調査の位置づけ（修正No.1）です。仕様書４（3）の対象4調査に含まれず、仕様書は新たな調査の企画・設計・配布・回収・入力・督促を行わないと定めています。現在の資料は、この調査で供給可能量・人材・受入困難・休廃止意向・ICT・BCPを把握する前提で工程を組んでいるため、実施されない場合にこれらの把握手段がすべて失われます。</t>
+          <t>13章立て・22表の構成は適切です。会議の流れ（位置付け→業務→評価→調査→分析→見込量→協議→工程→成果物→確認事項→個人情報）に沿っており、この構成を変える必要はありません。</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -812,12 +825,12 @@
     <row r="14" ht="72" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>解消済みの論点</t>
+          <t>最も急ぐ修正</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>「令和8年実績で再基準化する」という工程（修正No.2）は、推計方法の変更により不要となりました。令和7年度の実績人口に社人研推計の階級別の伸び率を乗じる方法に改め、基準年度の推計値が実績1,984人と一致します。資料のまま会議に諮ると、解決済みの論点に時間を使うことになります。</t>
+          <t>事業所実態調査の位置づけ（修正No.1）です。仕様書４（3）の対象4調査に含まれず、仕様書は新たな調査の企画・設計・配布・回収・入力・督促を行わないと定めています。現在の資料は、この調査で供給可能量・人材・受入困難・休廃止意向・ICT・BCPを把握する前提で工程を組んでいるため、実施されない場合にこれらの把握手段がすべて失われます。</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -827,12 +840,12 @@
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>青枠について</t>
+          <t>解消済みの論点</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>全件削除は推奨しません。8箇所のうち、アジェンダ（表0）とまとめ（表21）は会議資料の骨格として必要です。一方、確認事項（表9）とレビュールール（表14）はその場で回答・合意を記録する性格のものであり、ヒアリングシートへ移す方が実効的です。残る4箇所は本文との重複又は工程表との一体化により解消できます。</t>
+          <t>「令和8年実績で再基準化する」という工程（修正No.2）は、推計方法の変更により不要となりました。令和7年度の実績人口に社人研推計の階級別の伸び率を乗じる方法に改め、基準年度の推計値が実績1,984人と一致します。資料のまま会議に諮ると、解決済みの論点に時間を使うことになります。</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -842,64 +855,64 @@
     <row r="16" ht="72" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ヒアリングシート</t>
+          <t>青枠について</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>別冊として作成しました（第10期計画_キックオフ会議ヒアリングシート.docx）。12項目について、確認内容・選択肢・記入欄・決定されない場合の影響を1項目1枠で構成しています。会議中に記入いただき、そのまま記録として残る形式です。</t>
+          <t>全件削除は推奨しません。8箇所のうち、アジェンダ（表0）とまとめ（表21）は会議資料の骨格として必要です。一方、確認事項（表9）とレビュールール（表14）はその場で回答・合意を記録する性格のものであり、ヒアリングシートへ移す方が実効的です。残る4箇所は本文との重複又は工程表との一体化により解消できます。</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="8" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリングシート</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>別冊として作成しました（第10期計画_キックオフ会議ヒアリングシート.docx）。12項目について、確認内容・選択肢・記入欄・決定されない場合の影響を1項目1枠で構成しています。会議中に記入いただき、そのまま記録として残る形式です。</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="8" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>【反映の結果（令和8年7月31日）】</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="88" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>ご指示</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>①事業所実態調査は仕様書に基づき削除、②再基準化は解消済みのため削除、③調整済認定率18.4％は撤回済みで了承、青枠は全件削除ではなく推奨の仕分けにより修正。</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="8" t="n"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="88" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>作成した資料</t>
+          <t>ご指示</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>キックオフ会議資料 第3稿（第10期計画_キックオフ会議資料_第3稿.docx）。94段落18表。青枠は8箇所から2箇所（アジェンダ・まとめ）へ。</t>
+          <t>①事業所実態調査は仕様書に基づき削除、②再基準化は解消済みのため削除、③調整済認定率18.4％は撤回済みで了承、青枠は全件削除ではなく推奨の仕分けにより修正。</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -907,14 +920,14 @@
       <c r="E21" s="8" t="n"/>
     </row>
     <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>①の反映</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>作成した資料</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>6章の表題を「調査結果・事業所実態調査の活用方針」から「調査結果の活用方針」に改め、仕様書４（3）の対象4調査と、新たな調査の企画・設計・配布・回収・入力及び督促を行わない旨を本文に明記した。表1・表4・表6・表8・表10・表11・表15・表16・表17及び会議後の重点行動から、同調査を前提とする記述を削除した。供給可能量・受入困難・休廃止縮小意向・ICT・BCPが同調査によらなければ把握できないことは6章に注記し、実施の要否をヒアリングシート項目1で確認する形とした。</t>
+          <t>キックオフ会議資料 第3稿（第10期計画_キックオフ会議資料_第3稿.docx）。94段落18表。青枠は8箇所から2箇所（アジェンダ・まとめ）へ。</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -924,12 +937,12 @@
     <row r="23" ht="88" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>②の反映</t>
+          <t>①の反映</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>7章の起点差の記述を削除し、階級別人口を実績人口×社人研推計の伸び率により求めることで基準年度の推計値が実績1,984人と一致する旨に改めた。8章の手順1・2、10章の工程表、まとめから「再基準化」の記述を削除した。あわせて認定者数の3シナリオの算定結果を7章に追加した。</t>
+          <t>6章の表題を「調査結果・事業所実態調査の活用方針」から「調査結果の活用方針」に改め、仕様書４（3）の対象4調査と、新たな調査の企画・設計・配布・回収・入力及び督促を行わない旨を本文に明記した。表1・表4・表6・表8・表10・表11・表15・表16・表17及び会議後の重点行動から、同調査を前提とする記述を削除した。供給可能量・受入困難・休廃止縮小意向・ICT・BCPが同調査によらなければ把握できないことは6章に注記し、実施の要否をヒアリングシート項目1で確認する形とした。</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -939,12 +952,12 @@
     <row r="24" ht="88" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>③の反映</t>
+          <t>②の反映</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>5章に「第10期KPIの基本案」の表を新設し（青枠 表7からの格上げ）、H01の測定指標を見える化W144（9.25％）とすること、18.4％はB5-a【注目する地域のみ】系列で全国・北海道と比較できないため撤回したことを明記した。表7（分析領域）・表12（成果物）の記述も改めた。</t>
+          <t>7章の起点差の記述を削除し、階級別人口を実績人口×社人研推計の伸び率により求めることで基準年度の推計値が実績1,984人と一致する旨に改めた。8章の手順1・2、10章の工程表、まとめから「再基準化」の記述を削除した。あわせて認定者数の3シナリオの算定結果を7章に追加した。</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -954,12 +967,12 @@
     <row r="25" ht="88" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>青枠の反映</t>
+          <t>③の反映</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>残す2（表0 アジェンダ・表21 まとめ。内容を更新）、格上げ1（表7 KPIの基本案 → 5章の通常の表）、本文へ統合3（表3 整合の基本方針 → 3章本文、表5 進め方の原則 → 4章本文、表12 12月までに必要な状態 → 10章の注）、ヒアリングシートへ移行2（表9 → 6章に参照を記載、表14 → 9章に参照を記載）。</t>
+          <t>5章に「第10期KPIの基本案」の表を新設し（青枠 表7からの格上げ）、H01の測定指標を見える化W144（9.25％）とすること、18.4％はB5-a【注目する地域のみ】系列で全国・北海道と比較できないため撤回したことを明記した。表7（分析領域）・表12（成果物）の記述も改めた。</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -967,22 +980,37 @@
       <c r="E25" s="8" t="n"/>
     </row>
     <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>中6件・軽微3件</t>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>青枠の反映</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+          <t>残す2（表0 アジェンダ・表21 まとめ。内容を更新）、格上げ1（表7 KPIの基本案 → 5章の通常の表）、本文へ統合3（表3 整合の基本方針 → 3章本文、表5 進め方の原則 → 4章本文、表12 12月までに必要な状態 → 10章の注）、ヒアリングシートへ移行2（表9 → 6章に参照を記載、表14 → 9章に参照を記載）。</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="8" t="n"/>
     </row>
-    <row r="28" ht="104" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>中6件・軽微3件</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」に主張ごとに示しています。</t>
         </is>
@@ -990,20 +1018,20 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
@@ -2797,4 +2825,604 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第3稿のレッドチームレビュー（12件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>受託者が作成した第3稿を、意図的に批判的な立場から点検した。記述ルール（主張の根拠水準の棚卸し07シート）に照らし、推論・仮説を断定形で記述している箇所、根拠の水準に見合わない記述、内部の不整合を洗い出した。12件すべてを第3稿に反映済みである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>指摘</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>改めた記述</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>表4 段階2（第9期評価）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>「自己点検（レッドチームレビュー）で29件を指摘し記述を訂正」。29件すべてを訂正したと読める。実際は訂正（指摘的中）5件・対応済14件・対応中7件・確認待ち1件・未対応2件である。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>「29件を指摘し、うち5件は資料の受領により指摘が的中したため評価の記述を訂正」に改めた。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>自己点検の成果を過大に述べている。「1件も〜ない」型の全称の記述を避けるという記述ルールと同じ問題である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>7章 主要論点、青枠 まとめ</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>「給付の22〜37％相当が区域外の事業所に向かっている」。22〜37％は6区分の自給率の単純平均から算定した値であり、給付額による加重平均ではない。「給付の」「相当」と付けると金額ベースの主張に読める。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>「区域外の事業所による給付の割合（施設・居住系で23〜35％）」に改め、まとめには「給付額による加重平均の算定には町別のサービス区分別給付費を要します」を加えた。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析06シートで、金額換算には町別のサービス区分別給付費を要すると明記している。会議資料でその留保を落とすと、確定していない金額の主張として受け取られる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>表4 基盤整備、青枠 まとめ</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>「3町の自給率は6区分平均で63〜78％」。東川町・東神楽町は多機能系が算定できないため5区分の平均である。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>「算定できる区分の単純平均」に改めた。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>「6区分平均」と書くと6区分すべてで算定できたことになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>表7 財政・保険料</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>「第10期給付費92.67億円（自然体）、自然体保険料6,238円」。いずれも認定者数の推計方法を変える前の自然体推計による値であり、新推計と整合しているように読める。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>「いずれも第2稿までの自然体推計による参考値」と明記し、「第2段階・第3段階の完了後に再算定する」を加えた。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>第1段階で認定者数の推計方法を変えたため、給付費・保険料も変わる。第2段階が未了で新しい値がないことを示さないと、旧値が確定値として扱われる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>8章 本文</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>「自然体推計確認シートは公表値6時点と差額0円で整合を確認しました。将来推計は…第1段階を完了しています」と並べて記述しており、同じ推計の話に読める。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>段落を分け、「これは同システムの計算過程の検算であり、上記の第1段階の推計とは別のものです」と明記した。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>検算の対象と推計の対象が異なる。並べると、第1段階の推計も公表値と差額0円で一致すると誤読される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>8章 表9 手順2、10章 表11 工程表</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>認定率のシナリオの決定時期が、8章では「8〜10月」、10章では「8月中旬〜下旬」と食い違う。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>8章を「10月中」、10章の該当作業を10月の行へ移した。ヒアリングシート項目6の「令和8年10月中」と統一した。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>同一の資料内で時期が2通りあると、どちらを前提に準備すればよいか分からない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>11章 本文</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>「現時点の成果品は26件」。第3稿自体を加えると27件であり、資料の中で自己言及がずれる。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>件数を書かず「成果品の内容、読む順序及び仕様書４（10）の納品物との対応は別冊『成果品一覧』に整理しています」に改めた。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>成果品は今後も増える。資料に件数を書くと、更新のたびに食い違いが生じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>表6 介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>「計画への活用：供給可能量、人材確保、生産性」。介護人材実態調査は施設の職員に関する調査であり、受入余力・受入不可・休廃止意向は把握できない。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>「人材確保、生産性。受入余力・受入不可・休廃止意向は本調査では把握できない」に改めた。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>6章の末尾で同じことを注記しているが、表の活用欄が過大なままだと、同調査で供給可能量まで把握できると受け取られる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>6章 本文、12章 表14</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>「事業所実態調査の実施の要否をご確認ください」。仕様書が受託者は行わないと定めている以上、受託者が実施の要否を問うのは筋が違う。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>「発注者において実施される予定があるか、実施される場合に受託者が集計・分析を行うか（業務範囲の追加となります）」に改めた。12章の確認事項も「事業所を対象とする調査の実施の予定と、受託者の関与の範囲」に改めた。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>問いの立て方が、受託者が業務範囲を決める立場にあるように見える。決めるのは発注者であり、受託者が確認するのは関与の範囲である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>表4 保険料・財政</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>「第9期は2年で月額385円の剰余」に留保がない。令和6年度はR7/2月、令和7年度はR8/1月サービス提供分までの集計である。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>「（令和6・7年度は年度途中までの集計）」を加えた。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>年度確定値により再計算すると値が変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>12章 表15（次回協議日等）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリングシート項目2・項目3と重複している。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>「内容はヒアリングシート項目2・項目3の結果を転記するものです」と位置づけを明記した。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>重複そのものは会議の締めくくりとして有用であるが、位置づけを書かないと二重に確認することになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>表7 認定・給付</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>「W144 9.25％」「1人当たり給付月額26,885円」の時点が書かれていない。W144は令和5年、給付月額は令和7年度である。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>それぞれ時点を併記し、「第1号被保険者1人当たり給付月額」と主語を明示した。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>同じ表の中で時点の異なる値が並ぶため、時点を書かないと同一時点の値として読まれる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>No.1 「自己点検（レッドチームレビュー）で29件を指摘、No.2 「給付の22〜37％相当が区域外の事業所に向かっ</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>No.3 「3町の自給率は6区分平均で63〜78％」。東川、No.4 「第10期給付費92.67億円（自然体）、自然体、No.5 「自然体推計確認シートは公表値6時点と差額0円で、No.6 認定率のシナリオの決定時期が、8章では「8〜10、No.7 「現時点の成果品は26件」。第3稿自体を加えると、No.8 「計画への活用：供給可能量、人材確保、生産性」。、No.9 「事業所実態調査の実施の要否をご確認ください」。</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>No.10 「第9期は2年で月額385円の剰余」に留保がない、No.11 ヒアリングシート項目2・項目3と重複している。、No.12 「W144 9.25％」「1人当たり給付月額26</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>【この再レビューで見えたこと】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>12件のうち5件（No.2・No.3・No.4・No.8・No.10）は、分析資料では留保を付けていたのに、会議資料に転記する際に留保が落ちたものです。資料を短くまとめる過程で、確定していない部分が確定したように見える記述に変わっています。</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2件（No.1・No.9）は、受託者の作業や立場を実際より強く述べたものです。「29件を訂正」「実施の要否を確認」は、いずれも受託者ができること・決められることを過大に示しています。</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2件（No.6・No.7）は資料内部の不整合です。同じ事項の時期が2通りある、自己言及の件数がずれるといった類のもので、資料を更新するたびに生じます。件数のように必ずずれるものは、資料に書かない方が確実です。</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>残る3件（No.5・No.11・No.12）は、異なる性格のものを並べたことによる誤読の余地です。検算と推計、重複する表、時点の異なる数値を、区別せずに並べていました。</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>注1）12件はいずれも第3稿に反映済みです。反映後の第3稿は96段落18表であり、禁止する記述（「〜に由来する」「〜と整合する」等）は0件です。注2）本シートは受託者による自己点検であり、外部の第三者によるレビューではありません。受託者が気づいていない前提の誤りは検出できません。注3）分析資料から会議資料へ転記する際に留保が落ちる問題（5件）は、今後も同じ形で生じます。会議資料・委員会資料を作成する際は、元の分析資料の注記を照合する手順を業務工程管理表に位置づけます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -997,32 +997,61 @@
     <row r="27" ht="88" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>中6件・軽微3件</t>
+          <t>ご指示（追加・令和8年8月3日）</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+          <t>「まだキックオフが終わっていないため、見える化システムによることは決定ではない。受託者として、仕様書に記載のとおり業務工程の都度発注者の意向を確認していく」旨のご指示をいただいた。</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="8" t="n"/>
     </row>
-    <row r="29" ht="104" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>追加のご指示の反映</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>全成果品から「令和8年7月30日に決定した」旨の記述を削除し、「受託者の案として仮に置き、キックオフ会議でご意向を確認する」旨に改めた。対象は、キックオフ会議資料（2章・4章・7章・8章の手順1・12章・まとめ・会議後の重点行動）、ヒアリングシート項目6（項目6-1として人口推計の基礎の選択肢を明示）、将来推計（00・01シート）、計画素案の別管理表（B5）、業務工程管理表（(5)将来推計・全体総括）、必要事項の一覧（方針No.1・資料No.9・No.14・進捗率・依存関係）、成果品一覧、確認事項メモ第9版の追記、計画素案の該当3箇所（［要協議］を付与）である。あわせてキックオフ会議資料の2章に、仕様書の定めにより各工程でその都度ご意向を確認する旨と、本資料の推計の前提等は受託者の案又は作業上の前提であって決定した事項ではない旨を明記した。</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>中6件・軽微3件</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="31" ht="104" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」に主張ごとに示しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B21:E21"/>
@@ -1031,7 +1060,10 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B29:E29"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
@@ -1398,7 +1430,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>その後に受領した資料と決定を反映するため。</t>
+          <t>その後に受領した資料と作業の進捗を反映するため。</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1667,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>会議資料の骨格である。参加者が最初に見て、何が議題かを把握するためのもの。ただし内容は第10稿・受領済み資料・決定事項に合わせて更新する。</t>
+          <t>会議資料の骨格である。参加者が最初に見て、何が議題かを把握するためのもの。ただし内容は第10稿・受領済み資料・確認事項の状況に合わせて更新する。</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2446,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>階級別認定率のシナリオの選択</t>
+          <t>人口推計の基礎の採用及び階級別認定率のシナリオの選択</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>①現状固定／②トレンド継続（受託者の推奨）／③令和元年水準へ回帰。令和11年度の認定者数は①2,044人・②2,004人・③2,112人。②を基本とし③を保険料の安全側の確認として併用する案。</t>
+          <t>人口推計の基礎は社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて試算している（ご意向を確認する）。認定率は①現状固定／②トレンド継続（受託者の推奨）／③令和元年水準へ回帰。令和11年度の認定者数は①2,044人・②2,004人・③2,112人。②を基本とし③を保険料の安全側の確認として併用する案。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1027,45 +1027,77 @@
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>中6件・軽微3件</t>
+          <t>実施済み3調査の受領（令和8年8月4日）</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）を受領した。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件、事業所への照会により解消できる事項が19件、様式・網羅性に関する事項が7件ある（別冊「実施済み3調査の受領点検と集計」）。</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="8" t="n"/>
     </row>
-    <row r="31" ht="104" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>3調査の反映</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大3件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿（令和8年8月4日現在）とした。</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>中6件・軽微3件</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>いずれも反映済み。計画素案第8稿→第10稿、「モデル利用65人」→「自然体推計の令和8年度基準値の利用者65人（104.8％）」及びスクリーニング値である旨の注記、訪問介護55.4→「受給者1人当たり利用回数55.4回／月（全国29.7回の1.87倍）」、成果物名を成果品一覧に統一、受領資料の一覧を「必要事項の一覧」へ集約、委員会日程が未確定である旨の注記、日付と版（令和8年7月31日・第3稿）、受領済み8系列の反映、個人情報の記述の現状への更新。</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="33" ht="104" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」に主張ごとに示しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A2:E2"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B15:E15"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="B25:E25"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）を受領した。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件、事業所への照会により解消できる事項が19件、様式・網羅性に関する事項が7件ある（別冊「実施済み3調査の受領点検と集計」）。</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（23の法人・事業者、102ファイル）を受領した。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が4件、事業所への照会により解消できる事項が19件、様式・網羅性に関する事項が8件ある（別冊「実施済み3調査の受領点検と集計」）。</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大3件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿（令和8年8月4日現在）とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大4件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿（令和8年8月4日現在）とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大4件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿（令和8年8月4日現在）とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大4件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>「必要事項の一覧」（8シート）に集約済みである旨を記載し、資料内の一覧は概要にとどめる。資料14件・決定17件・日程6件・成果品7件・告示待ち5件・受託者の作業7件に整理している。</t>
+          <t>「必要事項の一覧」（8シート）に集約済みである旨を記載し、資料内の一覧は概要にとどめる。資料15件・決定19件・日程6件・成果品7件・告示待ち5件・受託者の作業8件に整理している。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大4件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とし、北海道の施設・住まいの名簿8種及び介護サービス情報公表システムの個別公表画面との突合による供給量の是正を反映して第6稿（令和8年8月5日現在）とした。ヒアリングシートは項目14（施設・住まいの供給量と調査の配布範囲）を加えて14項目・110分とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ご提供いただいたキックオフ会議資料（更新版・令和8年7月27日現在・第2稿）を、現時点の作業状況及び業務仕様書と照合しました。修正が必要な箇所12件（重大3・中6・軽微3）を確認しました。青枠の注記8箇所については、全件削除ではなく性格別の仕分けを提案し、ご了承をいただきました。12件すべてと青枠の仕分けを反映した第3稿を作成しています。作成日：令和8年7月31日。</t>
+          <t>ご提供いただいたキックオフ会議資料（更新版・令和8年7月27日現在・第2稿）を、現時点の作業状況及び業務仕様書と照合しました。修正が必要な箇所12件（重大3・中6・軽微3）を確認しました。青枠の注記8箇所については、全件削除ではなく性格別の仕分けを提案し、ご了承をいただきました。12件すべてと青枠の仕分けを反映した第3稿を作成し、その後の資料の受領に合わせて第4稿・第5稿・第6稿へ更新しました。作成日：令和8年7月31日（第6稿までの経緯を令和8年8月5日に追記）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とし、北海道の施設・住まいの名簿8種及び介護サービス情報公表システムの個別公表画面との突合による供給量の是正を反映して第6稿（令和8年8月5日現在）とした。ヒアリングシートは項目14（施設・住まいの供給量と調査の配布範囲）を加えて14項目・110分とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とし、北海道の施設・住まいの名簿8種及び介護サービス情報公表システムの個別公表画面との突合による供給量の是正を反映して第6稿（令和8年8月5日現在）とした。ヒアリングシートは項目14（施設・住まいの供給量と調査の配布範囲）を加えて16項目・120分とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大5件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とし、北海道の施設・住まいの名簿8種及び介護サービス情報公表システムの個別公表画面との突合による供給量の是正を反映して第6稿（令和8年8月5日現在）とした。ヒアリングシートは項目14（施設・住まいの供給量と調査の配布範囲）を加えて16項目・120分とした。</t>
+          <t>第2章（調査結果の活用方針）の記述を第10期分の受領後の状況に改め、施設への入所前の居場所（病院・診療所57.0％）、退去先、介護職員348人・介護福祉士67.1％等を会議資料に反映した。点検事項の重大6件はヒアリングシート項目13としてご意向を確認する形とした。これに伴い会議資料を第4稿とし、さらに将来推計の第2段階の試算を反映して第5稿（令和8年8月4日現在）とし、北海道の施設・住まいの名簿8種及び介護サービス情報公表システムの個別公表画面との突合による供給量の是正を反映して第6稿（令和8年8月5日現在）とした。ヒアリングシートは項目14（施設・住まいの供給量と調査の配布範囲）を加えて16項目・120分とした。</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_青枠の注記の扱い" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_業務範囲との齟齬" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ヒアリングシートへ移す事項" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_第3稿のレッドチームレビュー" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_第3稿の自己点検記録" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>05_第3稿のレッドチームレビュー</t>
+          <t>05_第3稿の自己点検記録</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>「計画素案第10稿」に改める。第10稿では、第2章に供給構造・利用率・交付金評価の節、第2章第3節に自給率の項、第3章に交付金評価の節と長期でみた到達点、第6章第1節に認定者数の3シナリオを新設している。</t>
+          <t>「計画素案」に改める。第10稿では、第2章に供給構造・利用率・交付金評価の節、第2章第3節に自給率の項、第3章に交付金評価の節と長期でみた到達点、第6章第1節に認定者数の3シナリオを新設している。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第3稿のレッドチームレビュー（12件）</t>
+          <t>第3稿の自己点検記録（12件）</t>
         </is>
       </c>
     </row>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>「自己点検（レッドチームレビュー）で29件を指摘し記述を訂正」。29件すべてを訂正したと読める。実際は訂正（指摘的中）5件・対応済14件・対応中7件・確認待ち1件・未対応2件である。</t>
+          <t>「自己点検（自己点検記録）で29件を指摘し記述を訂正」。29件すべてを訂正したと読める。実際は訂正（指摘のとおり）5件・対応済14件・対応中7件・確認待ち1件・未対応2件である。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>「29件を指摘し、うち5件は資料の受領により指摘が的中したため評価の記述を訂正」に改めた。</t>
+          <t>「29件を指摘し、うち5件は資料の受領により指摘のとおりであることが確認されたため評価の記述を訂正」に改めた。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>No.1 「自己点検（レッドチームレビュー）で29件を指摘、No.2 「給付の22〜37％相当が区域外の事業所に向かっ</t>
+          <t>No.1 「自己点検（自己点検記録）で29件を指摘し記述を、No.2 「給付の22〜37％相当が区域外の事業所に向かっ</t>
         </is>
       </c>
       <c r="D19" s="7" t="n"/>

--- a/output/第10期計画_キックオフ資料の点検結果.xlsx
+++ b/output/第10期計画_キックオフ資料の点検結果.xlsx
@@ -1072,7 +1072,7 @@
     <row r="33" ht="104" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「主張の根拠水準の棚卸しと再レビュー」に主張ごとに示しています。</t>
+          <t>注1）本点検は、資料の内容が現時点の作業状況及び仕様書と一致しているかを確認したものです。資料の構成・分量・体裁については、会議の進め方に関わるため発注者のご判断によります。注2）修正No.1（事業所実態調査）は、資料の修正にとどまらず業務範囲の確認を伴います。会議の前に方針をご確認いただくことをお願いいたします。注3）本資料に記載した現時点の数値は、「成果品一覧」に掲げる各分析資料に基づいています。根拠の水準は「受託者の自己点検」に主張ごとに示しています。</t>
         </is>
       </c>
     </row>
